--- a/MK spesialisasi.xlsx
+++ b/MK spesialisasi.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sai/Code/Peralihan TB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AEE6E74-3214-1A4C-9E73-21B63E519F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AEA179B-5579-014D-BC90-3D4DC8953BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4420" yWindow="1660" windowWidth="24980" windowHeight="16160" activeTab="1" xr2:uid="{DF98AB3D-F219-A347-BF98-3FC0F5445947}"/>
+    <workbookView xWindow="3700" yWindow="5160" windowWidth="24980" windowHeight="16160" activeTab="1" xr2:uid="{DF98AB3D-F219-A347-BF98-3FC0F5445947}"/>
   </bookViews>
   <sheets>
     <sheet name="MK Pilihan" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Konversi" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="280">
   <si>
     <t>Klaster MK Pilihan</t>
   </si>
@@ -268,13 +268,723 @@
   <si>
     <t>Pembelajaran Multidisiplin 2 
 (Multidisciplinary Learning 2)</t>
+  </si>
+  <si>
+    <r>
+      <t>Kurikulum 2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFF5F5F5"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Sem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Kode MK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Nama MK 2021</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SKS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Nama MK Baru</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>1 </t>
+  </si>
+  <si>
+    <t>TKU211131 </t>
+  </si>
+  <si>
+    <t>Pemrograman Dasar </t>
+  </si>
+  <si>
+    <t>3 </t>
+  </si>
+  <si>
+    <t>TBM261107 </t>
+  </si>
+  <si>
+    <t>2 </t>
+  </si>
+  <si>
+    <t>TKU211102 </t>
+  </si>
+  <si>
+    <t>Matematika Diskrit </t>
+  </si>
+  <si>
+    <t>TBM262101 </t>
+  </si>
+  <si>
+    <t>TKU211104 </t>
+  </si>
+  <si>
+    <t>Teori Vektor dan Matriks </t>
+  </si>
+  <si>
+    <t>TKF261103 </t>
+  </si>
+  <si>
+    <t>Aljabar Linear </t>
+  </si>
+  <si>
+    <t>TKU211202 </t>
+  </si>
+  <si>
+    <t>TKU211101 </t>
+  </si>
+  <si>
+    <t>Kalkulus Variabel Tunggal </t>
+  </si>
+  <si>
+    <t>TKF261102 </t>
+  </si>
+  <si>
+    <t>Kalkulus </t>
+  </si>
+  <si>
+    <t>TKU211121 </t>
+  </si>
+  <si>
+    <t>Fisika Mekanika Klasik </t>
+  </si>
+  <si>
+    <t>TKF261105 </t>
+  </si>
+  <si>
+    <t>Fisika Dasar </t>
+  </si>
+  <si>
+    <t>TKU211122 </t>
+  </si>
+  <si>
+    <t>Fisika Fluida, Kalor, dan Gelombang </t>
+  </si>
+  <si>
+    <t>TBM261204 </t>
+  </si>
+  <si>
+    <t>Fenomena Biotransport </t>
+  </si>
+  <si>
+    <t>TKB211101 </t>
+  </si>
+  <si>
+    <t>Kimia Dasar </t>
+  </si>
+  <si>
+    <t>TKF261104 </t>
+  </si>
+  <si>
+    <t>TKU212142 </t>
+  </si>
+  <si>
+    <t>Teknik Digital </t>
+  </si>
+  <si>
+    <t>4 </t>
+  </si>
+  <si>
+    <t>TBM262201 </t>
+  </si>
+  <si>
+    <t>Teknik Digital dan Mikroposesor </t>
+  </si>
+  <si>
+    <t>TKU212244 </t>
+  </si>
+  <si>
+    <t>Sistem Mikroprosesor </t>
+  </si>
+  <si>
+    <t>TKU211131P </t>
+  </si>
+  <si>
+    <t>Prakt. Pemrograman Dasar </t>
+  </si>
+  <si>
+    <t>TBM261209 </t>
+  </si>
+  <si>
+    <t>TKB211201 </t>
+  </si>
+  <si>
+    <t>Biologi </t>
+  </si>
+  <si>
+    <t>TBM261207 </t>
+  </si>
+  <si>
+    <t>Biologi Sel dan Genetika </t>
+  </si>
+  <si>
+    <t>FIU211201 </t>
+  </si>
+  <si>
+    <t>Konsep Keteknikan untuk Peradaban </t>
+  </si>
+  <si>
+    <t>TKF261208 </t>
+  </si>
+  <si>
+    <t>TKU211103 </t>
+  </si>
+  <si>
+    <t>Kalkulus Variabel Jamak </t>
+  </si>
+  <si>
+    <t>TBM261202 </t>
+  </si>
+  <si>
+    <t>TKU211201 </t>
+  </si>
+  <si>
+    <t>Analisis Variabel Kompleks </t>
+  </si>
+  <si>
+    <t>TKU211221 </t>
+  </si>
+  <si>
+    <t>Fisika Listrik dan Magnet </t>
+  </si>
+  <si>
+    <t>TBM261205 </t>
+  </si>
+  <si>
+    <t>Fisika Listrik, Magnet dan Gelombang </t>
+  </si>
+  <si>
+    <t>TKU211211 </t>
+  </si>
+  <si>
+    <t>Probabilitas dan Variabel Acak </t>
+  </si>
+  <si>
+    <t>TBM261101 </t>
+  </si>
+  <si>
+    <t>TKU212101 </t>
+  </si>
+  <si>
+    <t>Metode Numeris </t>
+  </si>
+  <si>
+    <t>TBM262104 </t>
+  </si>
+  <si>
+    <t>TKU212111 </t>
+  </si>
+  <si>
+    <t>Statistika </t>
+  </si>
+  <si>
+    <t>TBM261201 </t>
+  </si>
+  <si>
+    <t>TKU212141 </t>
+  </si>
+  <si>
+    <t>Isyarat dan Sistem </t>
+  </si>
+  <si>
+    <t>TBM262202 </t>
+  </si>
+  <si>
+    <t>TKU212143 </t>
+  </si>
+  <si>
+    <t>Analisis Untai Elektrik DC </t>
+  </si>
+  <si>
+    <t>TBM262106 </t>
+  </si>
+  <si>
+    <t>TKU212144 </t>
+  </si>
+  <si>
+    <t>Telekomunikasi Dasar </t>
+  </si>
+  <si>
+    <t>TKU212121P </t>
+  </si>
+  <si>
+    <t>Prakt. Sains Dasar </t>
+  </si>
+  <si>
+    <t>TBM262108 </t>
+  </si>
+  <si>
+    <t>TKU211203 </t>
+  </si>
+  <si>
+    <t>Persamaan Differensial </t>
+  </si>
+  <si>
+    <t>TBM262102 </t>
+  </si>
+  <si>
+    <t>TKU211231 </t>
+  </si>
+  <si>
+    <t>Algoritma dan Struktur Data </t>
+  </si>
+  <si>
+    <t>TBM262203 </t>
+  </si>
+  <si>
+    <t>Algoritma Struktur Data </t>
+  </si>
+  <si>
+    <t>TKU212242 </t>
+  </si>
+  <si>
+    <t>Elektronika Dasar </t>
+  </si>
+  <si>
+    <t>TBM262105 </t>
+  </si>
+  <si>
+    <t>TKU212243 </t>
+  </si>
+  <si>
+    <t>Teknik Kendali </t>
+  </si>
+  <si>
+    <t>5 </t>
+  </si>
+  <si>
+    <t>TBM263101 </t>
+  </si>
+  <si>
+    <t>Teknik Kendali Biomedis </t>
+  </si>
+  <si>
+    <t>TKU213141 </t>
+  </si>
+  <si>
+    <t>Jaringan Komunikasi dan Data </t>
+  </si>
+  <si>
+    <t>TKB212201 </t>
+  </si>
+  <si>
+    <t>Teknik Biomagnetika </t>
+  </si>
+  <si>
+    <t>TBM263105 </t>
+  </si>
+  <si>
+    <t>TKB213203 </t>
+  </si>
+  <si>
+    <t>Teknik Pengolahan Citra Biomedis </t>
+  </si>
+  <si>
+    <t>TBM263102 </t>
+  </si>
+  <si>
+    <t>Pengolahan Isyarat dan Citra Biomedis </t>
+  </si>
+  <si>
+    <t>TKB212202 </t>
+  </si>
+  <si>
+    <t>Teknik Pengolahan Isyarat Biomedis </t>
+  </si>
+  <si>
+    <t>TKB212203 </t>
+  </si>
+  <si>
+    <t>Pengukuran dan Instrumentasi Biomedis </t>
+  </si>
+  <si>
+    <t>TBM262204 </t>
+  </si>
+  <si>
+    <t>TKU213101 </t>
+  </si>
+  <si>
+    <t>Teknik Optimisasi </t>
+  </si>
+  <si>
+    <t>TKU213142 </t>
+  </si>
+  <si>
+    <t>Kerja Praktik </t>
+  </si>
+  <si>
+    <t>7 </t>
+  </si>
+  <si>
+    <t>TBM264102 </t>
+  </si>
+  <si>
+    <t>Magang Industri </t>
+  </si>
+  <si>
+    <t>TKB213101 </t>
+  </si>
+  <si>
+    <t>Elektronika Biomedis </t>
+  </si>
+  <si>
+    <t>TBM262205 </t>
+  </si>
+  <si>
+    <t>TKB213102 </t>
+  </si>
+  <si>
+    <t>Anatomi dan Fisiologi </t>
+  </si>
+  <si>
+    <t>TBM261106 </t>
+  </si>
+  <si>
+    <t>Anatomi Manusia </t>
+  </si>
+  <si>
+    <t>TBM261206 </t>
+  </si>
+  <si>
+    <t>Fisiologi Manusia </t>
+  </si>
+  <si>
+    <t>TKB213103 </t>
+  </si>
+  <si>
+    <t>Teknik Biomekanika </t>
+  </si>
+  <si>
+    <t>TKB213104 </t>
+  </si>
+  <si>
+    <t>Proyek Junior Teknik Biomedis </t>
+  </si>
+  <si>
+    <t>TBM262209 </t>
+  </si>
+  <si>
+    <t>TKB213105 </t>
+  </si>
+  <si>
+    <t>Sensor dan Transduser </t>
+  </si>
+  <si>
+    <t>TBM262206 </t>
+  </si>
+  <si>
+    <t>Sensor, Aktuator dan Antarmuka </t>
+  </si>
+  <si>
+    <t>6 </t>
+  </si>
+  <si>
+    <t>TKB213201 </t>
+  </si>
+  <si>
+    <t>Teknik Biomaterial </t>
+  </si>
+  <si>
+    <t>TBM262207 </t>
+  </si>
+  <si>
+    <t>TKB213202 </t>
+  </si>
+  <si>
+    <t>Teknik Pencitraan Biomedis </t>
+  </si>
+  <si>
+    <t>TBM263104 </t>
+  </si>
+  <si>
+    <t>TKB213204 </t>
+  </si>
+  <si>
+    <t>Proyek Perancangan Teknik Biomedis 1 </t>
+  </si>
+  <si>
+    <t>TBM264105 </t>
+  </si>
+  <si>
+    <t>TKB213205 </t>
+  </si>
+  <si>
+    <t>Proyek Senior Teknik Biomedis </t>
+  </si>
+  <si>
+    <t>TBM263109 </t>
+  </si>
+  <si>
+    <t>UNU21xxxx </t>
+  </si>
+  <si>
+    <t>Pilihan C/MBKM </t>
+  </si>
+  <si>
+    <t>TBM2632XX </t>
+  </si>
+  <si>
+    <t>Spesialisasi </t>
+  </si>
+  <si>
+    <t>FIU213201 </t>
+  </si>
+  <si>
+    <t>Pancasila </t>
+  </si>
+  <si>
+    <t>FIU262208 </t>
+  </si>
+  <si>
+    <t>UNU211101 </t>
+  </si>
+  <si>
+    <t>Bahasa Indonesia </t>
+  </si>
+  <si>
+    <t>UNU262107 </t>
+  </si>
+  <si>
+    <t>Bahasa Indonesia dan Komunikasi Profesional </t>
+  </si>
+  <si>
+    <t>UNU222002 </t>
+  </si>
+  <si>
+    <t>Komunikasi Masyarakat </t>
+  </si>
+  <si>
+    <t>UNU2641XX </t>
+  </si>
+  <si>
+    <t>UNU214202 </t>
+  </si>
+  <si>
+    <t>Kewarganegaraan </t>
+  </si>
+  <si>
+    <t>UNU263107 </t>
+  </si>
+  <si>
+    <t>FIU2121xx </t>
+  </si>
+  <si>
+    <t>Agama </t>
+  </si>
+  <si>
+    <t>FIU264103 </t>
+  </si>
+  <si>
+    <t>TKB214101 </t>
+  </si>
+  <si>
+    <t>Proyek Perancangan Teknik Biomedis 2 </t>
+  </si>
+  <si>
+    <t>8 </t>
+  </si>
+  <si>
+    <t>TBM264204 </t>
+  </si>
+  <si>
+    <t>UNU214101 </t>
+  </si>
+  <si>
+    <t>Kuliah Kerja Nyata </t>
+  </si>
+  <si>
+    <t>UNU222003 </t>
+  </si>
+  <si>
+    <t>Penerapan Teknologi Tepat Guna </t>
+  </si>
+  <si>
+    <t>UNU242033 </t>
+  </si>
+  <si>
+    <t>Literasi Kesehatan </t>
+  </si>
+  <si>
+    <t>TKF264202 </t>
+  </si>
+  <si>
+    <t>Literasi Kesehatan (K5L) </t>
+  </si>
+  <si>
+    <t>TKB21xxxx </t>
+  </si>
+  <si>
+    <t>Pilihan A/B </t>
+  </si>
+  <si>
+    <t>TKB2141xx </t>
+  </si>
+  <si>
+    <t>Pilihan B </t>
+  </si>
+  <si>
+    <t>UNU214201 </t>
+  </si>
+  <si>
+    <t>Studium Generale </t>
+  </si>
+  <si>
+    <t>TBM264203 </t>
+  </si>
+  <si>
+    <t>TKB2132xx </t>
+  </si>
+  <si>
+    <t>Pilihan A </t>
+  </si>
+  <si>
+    <t>TKU214241 </t>
+  </si>
+  <si>
+    <t>Skripsi &amp; Pendadaran </t>
+  </si>
+  <si>
+    <t>TBM263205 </t>
+  </si>
+  <si>
+    <t>Proyek Individu </t>
+  </si>
+  <si>
+    <t>TBM263103 </t>
+  </si>
+  <si>
+    <t>Kecerdasan Artifisial </t>
+  </si>
+  <si>
+    <t>TBM261108 </t>
+  </si>
+  <si>
+    <t>Pengantar Keilmuan Teknik Biomedis </t>
+  </si>
+  <si>
+    <t>UNU263108 </t>
+  </si>
+  <si>
+    <t>Digital Humanities </t>
+  </si>
+  <si>
+    <t>TBM263106 </t>
+  </si>
+  <si>
+    <t>Regulasi dan Standar Alat Kesehatan </t>
+  </si>
+  <si>
+    <t>TBM263204 </t>
+  </si>
+  <si>
+    <t>Etika Teknik Biomedis </t>
+  </si>
+  <si>
+    <t>TBM264201 </t>
+  </si>
+  <si>
+    <t>Kewirausahaan Biomedis </t>
+  </si>
+  <si>
+    <r>
+      <t>Total SKS Kurikulum 2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFF5F5F5"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>144</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFF5F5F5"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>K2026</t>
+  </si>
+  <si>
+    <t>K2021</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -309,6 +1019,41 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFF5F5F5"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -336,7 +1081,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -345,6 +1090,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1165,9 +1915,1663 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63D86AD5-FF80-A74C-8412-A67175F6B269}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" s="8"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A49" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A50" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A54" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A55" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A56" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A57" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="H57" s="8" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A58" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="H58" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="H59" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A60" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="H60" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A61" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="H61" s="8" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A62" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="H62" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A63" s="8"/>
+      <c r="B63" s="8"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="8"/>
+      <c r="E63" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="H63" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A64" s="8"/>
+      <c r="B64" s="8"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="H64" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A65" s="8"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="8"/>
+      <c r="E65" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="H65" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A66" s="8"/>
+      <c r="B66" s="8"/>
+      <c r="C66" s="8"/>
+      <c r="D66" s="8"/>
+      <c r="E66" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="H66" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A67" s="8"/>
+      <c r="B67" s="8"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="8"/>
+      <c r="E67" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="H67" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A68" s="8"/>
+      <c r="B68" s="8"/>
+      <c r="C68" s="8"/>
+      <c r="D68" s="8"/>
+      <c r="E68" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="H68" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C69" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A70" s="8"/>
+      <c r="B70" s="8"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>